--- a/data/trans_camb/P1421-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P1421-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,12</t>
+          <t>2,92</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,98</t>
+          <t>6,89</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5,12</t>
+          <t>4,98</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 0,64</t>
+          <t>-1,79; 0,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 1,54</t>
+          <t>-1,21; 1,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 5,2</t>
+          <t>1,18; 4,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,42; 7,2</t>
+          <t>2,65; 7,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,31</t>
+          <t>0,41; 4,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,77; 9,01</t>
+          <t>4,71; 9,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,5</t>
+          <t>0,69; 3,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,11; 2,46</t>
+          <t>0,09; 2,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,83; 6,67</t>
+          <t>3,75; 6,63</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>200,42%</t>
+          <t>187,44%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>298,68%</t>
+          <t>294,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>263,27%</t>
+          <t>255,73%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-79,18; 88,45</t>
+          <t>-78,73; 69,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-53,79; 173,68</t>
+          <t>-57,16; 201,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56,58; 584,07</t>
+          <t>45,94; 556,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66,58; 477,95</t>
+          <t>78,98; 464,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,31; 299,52</t>
+          <t>12,19; 300,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>143,95; 623,99</t>
+          <t>130,78; 595,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,26; 264,26</t>
+          <t>21,87; 231,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,37; 170,69</t>
+          <t>2,95; 173,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>148,75; 459,18</t>
+          <t>136,07; 455,79</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>1,24</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,44</t>
+          <t>4,54</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,14</t>
+          <t>2,92</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,75; -0,37</t>
+          <t>-2,66; -0,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,76; -0,41</t>
+          <t>-2,81; -0,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 2,23</t>
+          <t>-0,32; 3,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 1,38</t>
+          <t>-2,5; 1,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 2,78</t>
+          <t>-1,69; 2,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,51; 6,62</t>
+          <t>2,2; 6,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 0,13</t>
+          <t>-2,26; 0,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 0,79</t>
+          <t>-1,65; 0,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 3,59</t>
+          <t>1,55; 4,23</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>75,59%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-82,03; -14,22</t>
+          <t>-79,85; -13,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-84,01; -19,35</t>
+          <t>-83,25; -18,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-51,89; 110,73</t>
+          <t>-12,12; 174,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-39,47; 34,77</t>
+          <t>-39,35; 33,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-20,52; 65,01</t>
+          <t>-26,67; 62,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,13; 161,9</t>
+          <t>32,54; 153,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-48,2; 5,08</t>
+          <t>-50,53; 4,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-35,04; 26,17</t>
+          <t>-36,54; 24,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,59; 106,02</t>
+          <t>33,16; 134,22</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,61</t>
+          <t>2,49</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,67</t>
+          <t>6,77</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,53</t>
+          <t>4,65</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 0,25</t>
+          <t>-2,45; 0,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 0,88</t>
+          <t>-2,2; 0,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,65; 4,54</t>
+          <t>0,58; 4,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 0,92</t>
+          <t>-4,22; 1,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 0,48</t>
+          <t>-4,41; 0,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 7,53</t>
+          <t>3,87; 9,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 0,12</t>
+          <t>-2,67; 0,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 0,15</t>
+          <t>-2,66; 0,29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 5,65</t>
+          <t>2,84; 6,18</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>126,97%</t>
+          <t>121,13%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>100,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>105,48%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-82,6; 35,62</t>
+          <t>-82,81; 30,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-70,88; 71,9</t>
+          <t>-72,82; 58,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16,4; 343,78</t>
+          <t>10,49; 344,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-51,34; 16,97</t>
+          <t>-51,88; 25,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-52,77; 11,68</t>
+          <t>-53,52; 10,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-22,88; 126,74</t>
+          <t>46,76; 172,51</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-53,81; 3,16</t>
+          <t>-52,2; 7,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-50,06; 4,82</t>
+          <t>-50,55; 8,47</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11,65; 152,04</t>
+          <t>55,44; 173,69</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,63</t>
+          <t>2,28</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,35</t>
+          <t>4,71</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,64</t>
+          <t>3,6</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,79; -0,09</t>
+          <t>-2,82; -0,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,8; -0,14</t>
+          <t>-2,72; -0,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,65; 4,98</t>
+          <t>0,41; 4,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,14; -0,98</t>
+          <t>-5,36; -1,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 0,49</t>
+          <t>-4,2; 0,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,37; 7,1</t>
+          <t>2,35; 7,33</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,67; -0,91</t>
+          <t>-3,63; -1,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,04; -0,27</t>
+          <t>-3,06; -0,39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,77; 5,48</t>
+          <t>2,05; 5,3</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>63,77%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-72,63; -2,18</t>
+          <t>-71,99; -1,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-72,48; -5,05</t>
+          <t>-72,67; 4,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11,23; 195,64</t>
+          <t>7,45; 189,63</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-54,66; -13,2</t>
+          <t>-56,73; -14,99</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-45,11; 8,21</t>
+          <t>-45,95; 6,7</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,53; 100,91</t>
+          <t>24,15; 108,4</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-56,9; -18,28</t>
+          <t>-57,12; -21,71</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-46,99; -4,27</t>
+          <t>-46,95; -5,65</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>27,28; 109,54</t>
+          <t>30,24; 107,62</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2,02</t>
+          <t>2,15</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,8</t>
+          <t>5,56</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3,47</t>
+          <t>3,92</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,77; -0,49</t>
+          <t>-1,83; -0,58</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,61; -0,3</t>
+          <t>-1,59; -0,28</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,06</t>
+          <t>1,26; 3,11</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 0,71</t>
+          <t>-1,51; 0,76</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 0,83</t>
+          <t>-1,48; 0,88</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,88; 6,19</t>
+          <t>4,38; 6,66</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,44; -0,12</t>
+          <t>-1,45; -0,12</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 0,15</t>
+          <t>-1,28; 0,03</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,39; 4,48</t>
+          <t>3,2; 4,72</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>95,49%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-65,07; -22,94</t>
+          <t>-64,94; -27,81</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-59,54; -14,93</t>
+          <t>-58,43; -12,92</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>36,64; 154,57</t>
+          <t>44,88; 153,04</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-22,99; 13,71</t>
+          <t>-23,75; 15,3</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-23,12; 16,26</t>
+          <t>-23,44; 16,81</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>45,96; 117,27</t>
+          <t>65,81; 126,82</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-32,34; -3,4</t>
+          <t>-32,51; -3,11</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-27,76; 4,25</t>
+          <t>-29,17; 1,18</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>54,74; 119,5</t>
+          <t>70,81; 125,34</t>
         </is>
       </c>
     </row>
